--- a/gestionFondRotatif/backend/docs/dictionnaire_donnees_mmf.xlsx
+++ b/gestionFondRotatif/backend/docs/dictionnaire_donnees_mmf.xlsx
@@ -87,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -98,6 +98,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -815,504 +817,514 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>canton</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Identifiant technique</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>canton</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>nom</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>UNIQUE, NOT NULL</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Nom du canton — donnée de référence, module Paramétrage</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>canton</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>latitude</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>DECIMAL(10,7)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Géolocalisation du canton (demandée par le président)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>canton</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>DECIMAL(10,7)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Géolocalisation du canton (demandée par le président)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>canton</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT TRUE</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Permet de désactiver un canton plutôt que le supprimer (module Paramétrage) — un canton déjà référencé par des bénéficiaires ne doit jamais être supprimé.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>fonction</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Identifiant technique</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>fonction</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(30)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>UNIQUE, NOT NULL</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>PRESIDENT, VICE_PRESIDENT, SECRETAIRE, TRESORIER, COMMISSAIRE, MEMBRE — remplace le texte libre sur membre_comite</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>fonction</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>libelle</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Libellé lisible de la fonction</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>habilitation</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Identifiant technique</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>habilitation</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(50)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>UNIQUE, NOT NULL</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Code de la permission (ex. VALIDER_DEMANDE, CONSULTER_RAPPORT) — module Paramétrage / Administration</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>habilitation</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>libelle</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(150)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Libellé lisible de la permission</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>fonction_habilitation</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>fonction_id</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>PK, FK, NOT NULL</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>fonction.id</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Quelle fonction possède cette habilitation (liaison N..N)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>fonction_habilitation</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>habilitation_id</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>PK, FK, NOT NULL</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>habilitation.id</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Quelle habilitation est accordée à cette fonction (liaison N..N)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>parametre</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>Identifiant technique</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>parametre</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>cle</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>UNIQUE, NOT NULL</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>Clé du paramètre (ex. taux_majoration_remboursement) — module Paramétrage, confirmé par le président (voice du 17/07)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>parametre</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>valeur</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>VARCHAR(255)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>Valeur du paramètre, modifiable sans toucher au code</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>parametre</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>TEXT</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Description libre du paramètre</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>beneficiaire</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Identifiant technique</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>beneficiaire</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>utilisateur_id</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>UNIQUE, NOT NULL</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>utilisateur.id</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Héritage Beneficiaire → Utilisateur (relation 1-1)</t>
         </is>
       </c>
     </row>
@@ -1324,23 +1336,27 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>age_estime</t>
+          <t>utilisateur_id</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr"/>
+          <t>UNIQUE, NOT NULL</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>utilisateur.id</t>
+        </is>
+      </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Âge souvent approximatif sur le terrain (les bénéficiaires oublient parfois leur date de naissance exacte)</t>
+          <t>Héritage Beneficiaire → Utilisateur (relation 1-1)</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1368,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>activite</t>
+          <t>canton_id</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -1365,10 +1381,14 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr"/>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>canton.id</t>
+        </is>
+      </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Activité économique du bénéficiaire</t>
+          <t>Canton du membre du comité qui a enregistré le bénéficiaire, renseigné automatiquement à la création — sert à restreindre chaque membre du comité aux bénéficiaires de son propre canton, et à la vue agrégée par canton (Web, Responsable).</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1400,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>age_estime</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(10,7)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -1393,10 +1413,10 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n"/>
+      <c r="E33" s="3" t="inlineStr"/>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Géolocalisation du bénéficiaire — module 1 du cahier des charges</t>
+          <t>Âge souvent approximatif sur le terrain (les bénéficiaires oublient parfois leur date de naissance exacte)</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1428,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>activite</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(10,7)</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -1421,10 +1441,10 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n"/>
+      <c r="E34" s="3" t="inlineStr"/>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Géolocalisation du bénéficiaire — module 1 du cahier des charges</t>
+          <t>Activité économique du bénéficiaire</t>
         </is>
       </c>
     </row>
@@ -1436,111 +1456,107 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>statut_mmf</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>DECIMAL(10,7)</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT 'Nouveau'</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n"/>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Statut dans le cycle du programme MMF (Nouveau, EnAttente, Financé, RemboursementEnCours, Soldé) — recalculé automatiquement à chaque événement financier</t>
+          <t>Géolocalisation du bénéficiaire — module 1 du cahier des charges</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>membre_comite</t>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DECIMAL(10,7)</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n"/>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Géolocalisation du bénéficiaire — module 1 du cahier des charges</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>beneficiaire</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>statut_mmf</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT 'Nouveau'</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Statut dans le cycle du programme MMF (Nouveau, EnAttente, Financé, RemboursementEnCours, Soldé) — recalculé automatiquement à chaque événement financier</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>membre_comite</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>utilisateur_id</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>UNIQUE, NOT NULL</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>utilisateur.id</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Héritage MembreComite → Utilisateur</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>membre_comite</t>
-        </is>
-      </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>fonction</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr"/>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Rôle interne au comité : Président, Vice-président, Secrétaire, Trésorier, Commissaire aux comptes, Membre — confirmé par la responsable du fonds</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -1552,23 +1568,27 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>nom_canton</t>
+          <t>utilisateur_id</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr"/>
+          <t>UNIQUE, NOT NULL</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>utilisateur.id</t>
+        </is>
+      </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Canton rattaché au comité — décision actée : simple colonne, pas de table canton séparée</t>
+          <t>Héritage MembreComite → Utilisateur</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1600,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>date_integration</t>
+          <t>fonction_id</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -1593,10 +1613,14 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>fonction.id</t>
+        </is>
+      </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Date d'entrée dans le comité</t>
+          <t>Rôle interne au comité (Président, Vice-président, Secrétaire, Trésorier, Commissaire aux comptes, Membre) — normalisé en table fonction/habilitation (module Administration, gestion fine des permissions), plutôt qu'un texte libre comme prévu initialement.</t>
         </is>
       </c>
     </row>
@@ -1608,111 +1632,111 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>canton_id</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT TRUE</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>canton.id</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Permet de désactiver un membre sans le supprimer</t>
+          <t>Canton rattaché au membre du comité — normalisé en table canton séparée (portée par la carte des cantons, la répartition des remboursements, etc.), la décision initiale de rester en simple colonne texte a été révisée en cours de développement.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>responsable_fond_rotatif</t>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>membre_comite</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>date_integration</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr"/>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Date d'entrée dans le comité</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
+          <t>membre_comite</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT TRUE</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr"/>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Permet de désactiver un membre sans le supprimer</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
           <t>responsable_fond_rotatif</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>utilisateur_id</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>UNIQUE, NOT NULL</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>utilisateur.id</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Héritage ResponsableFondRotatif → Utilisateur</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>responsable_fond_rotatif</t>
-        </is>
-      </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>date_nomination</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr"/>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Date de prise de fonction</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -1724,107 +1748,111 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>utilisateur_id</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT TRUE</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr"/>
+          <t>UNIQUE, NOT NULL</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>utilisateur.id</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Permet de désactiver sans supprimer</t>
+          <t>Héritage ResponsableFondRotatif → Utilisateur</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>domaine</t>
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>responsable_fond_rotatif</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>date_nomination</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr"/>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Date de prise de fonction</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>domaine</t>
+          <t>responsable_fond_rotatif</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>actif</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>UNIQUE, NOT NULL</t>
+          <t>NOT NULL, DEFAULT TRUE</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Secteur d'activité : Environnement, Agriculture, Élevage, Pêche, Petit commerce, GHM — liste fournie par le président</t>
+          <t>Permet de désactiver sans supprimer</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>domaine</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr"/>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Description complémentaire du secteur</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -1836,107 +1864,107 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT TRUE</t>
+          <t>UNIQUE, NOT NULL</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Permet de désactiver un domaine sans le supprimer (table plutôt qu'énumération pour rester extensible)</t>
+          <t>Secteur d'activité : Environnement, Agriculture, Élevage, Pêche, Petit commerce, GHM — liste fournie par le président</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>vague</t>
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>domaine</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr"/>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Description complémentaire du secteur</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>vague</t>
+          <t>domaine</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>code_vague</t>
+          <t>actif</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>UNIQUE, NOT NULL</t>
+          <t>NOT NULL, DEFAULT TRUE</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr"/>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Référence métier (ex. VG-2025-01)</t>
+          <t>Permet de désactiver un domaine sans le supprimer (table plutôt qu'énumération pour rester extensible)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>vague</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr"/>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Nom de la campagne de financement</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -1948,23 +1976,23 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>code_vague</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>UNIQUE, NOT NULL</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr"/>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Description de la campagne</t>
+          <t>Référence métier (ex. VG-2025-01)</t>
         </is>
       </c>
     </row>
@@ -1976,12 +2004,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>date_debut</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -1992,7 +2020,7 @@
       <c r="E54" s="3" t="inlineStr"/>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Début de la vague</t>
+          <t>Nom de la campagne de financement</t>
         </is>
       </c>
     </row>
@@ -2004,23 +2032,23 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>date_fin</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr"/>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Fin de la vague</t>
+          <t>Description de la campagne</t>
         </is>
       </c>
     </row>
@@ -2032,23 +2060,23 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>budget_prevu</t>
+          <t>date_debut</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Budget prévisionnel de la campagne</t>
+          <t>Début de la vague</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2088,12 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>statut</t>
+          <t>date_fin</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -2076,7 +2104,7 @@
       <c r="E57" s="3" t="inlineStr"/>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Planifiée, En cours, Clôturée</t>
+          <t>Fin de la vague</t>
         </is>
       </c>
     </row>
@@ -2088,107 +2116,107 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>date_creation</t>
+          <t>budget_prevu</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DECIMAL(15,2)</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT CURRENT_TIMESTAMP</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr"/>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Date de création de l'enregistrement</t>
+          <t>Budget prévisionnel de la campagne</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>fond_rotatif</t>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>vague</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>statut</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr"/>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Planifiée, En cours, Clôturée</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>fond_rotatif</t>
+          <t>vague</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>code_fond</t>
+          <t>date_creation</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(30)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>UNIQUE, NOT NULL</t>
+          <t>NOT NULL, DEFAULT CURRENT_TIMESTAMP</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr"/>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Référence métier du fonds</t>
+          <t>Date de création de l'enregistrement</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>fond_rotatif</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>libelle_fond</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr"/>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Nom/libellé du fonds</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -2200,79 +2228,79 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>montant_fond</t>
+          <t>code_fond</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT 0</t>
+          <t>UNIQUE, NOT NULL</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr"/>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Solde disponible — stocké et mis à jour par transaction (débit à chaque Financement, crédit à chaque RemboursementCollectif confirmé)</t>
+          <t>Référence métier du fonds</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>programme</t>
+          <t>fond_rotatif</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>libelle_fond</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="n"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr"/>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Nom/libellé du fonds</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>programme</t>
+          <t>fond_rotatif</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>montant_fond</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>DECIMAL(15,2)</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>UNIQUE, NOT NULL</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n"/>
+          <t>NOT NULL, DEFAULT 0</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr"/>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Nom du programme (ex. COMDEKS4) — plusieurs programmes peuvent être actifs simultanément et financer le même fond rotatif (confirmé par le président)</t>
+          <t>Solde disponible — stocké et mis à jour par transaction (débit à chaque Financement, crédit à chaque RemboursementCollectif confirmé)</t>
         </is>
       </c>
     </row>
@@ -2284,23 +2312,23 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="E65" s="3" t="n"/>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Description libre du programme</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -2312,91 +2340,91 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>actif</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT TRUE</t>
+          <t>UNIQUE, NOT NULL</t>
         </is>
       </c>
       <c r="E66" s="3" t="n"/>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Permet de désactiver un programme sans le supprimer</t>
+          <t>Nom du programme (ex. COMDEKS4) — plusieurs programmes peuvent être actifs simultanément et financer le même fond rotatif (confirmé par le président)</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>demande_financement</t>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>programme</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n"/>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Description libre du programme</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
+          <t>programme</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT TRUE</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Permet de désactiver un programme sans le supprimer</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
           <t>demande_financement</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>code_demande</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>VARCHAR(30)</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>UNIQUE, NOT NULL</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>Référence métier (ex. DEM-2025-014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>demande_financement</t>
-        </is>
-      </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>membre_comite_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -2406,17 +2434,13 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>membre_comite.id</t>
-        </is>
-      </c>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr"/>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Le trésorier qui a initié la demande (niveau 0 du circuit)</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -2428,27 +2452,23 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>vague_id</t>
+          <t>code_demande</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(30)</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>vague.id</t>
-        </is>
-      </c>
+          <t>UNIQUE, NOT NULL</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr"/>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Campagne à laquelle la demande appartient — une vague peut recevoir plusieurs demandes de plusieurs comités</t>
+          <t>Référence métier (ex. DEM-2025-014)</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2480,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>domaine_id</t>
+          <t>membre_comite_id</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -2475,12 +2495,12 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>domaine.id</t>
+          <t>membre_comite.id</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Secteur d'activité concerné par la demande</t>
+          <t>Le trésorier qui a initié la demande (niveau 0 du circuit)</t>
         </is>
       </c>
     </row>
@@ -2492,12 +2512,12 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>objet_demande</t>
+          <t>vague_id</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -2505,10 +2525,14 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>vague.id</t>
+        </is>
+      </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Motif/objet de la demande, précisé par le président</t>
+          <t>Campagne à laquelle la demande appartient — une vague peut recevoir plusieurs demandes de plusieurs comités</t>
         </is>
       </c>
     </row>
@@ -2520,23 +2544,27 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>resultat_attendu</t>
+          <t>domaine_id</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>domaine.id</t>
+        </is>
+      </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Ce que les bénéficiaires s'engagent à produire s'ils obtiennent le financement</t>
+          <t>Secteur d'activité concerné par la demande</t>
         </is>
       </c>
     </row>
@@ -2548,23 +2576,23 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>periode_previsionnelle</t>
+          <t>objet_demande</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Période prévue pour l'activité financée</t>
+          <t>Motif/objet de la demande, précisé par le président</t>
         </is>
       </c>
     </row>
@@ -2576,12 +2604,12 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>site_travail</t>
+          <t>resultat_attendu</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(150)</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -2592,7 +2620,7 @@
       <c r="E75" s="3" t="inlineStr"/>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Lieu où se déroule l'activité</t>
+          <t>Ce que les bénéficiaires s'engagent à produire s'ils obtiennent le financement</t>
         </is>
       </c>
     </row>
@@ -2604,23 +2632,23 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>nb_femmes_benef</t>
+          <t>periode_previsionnelle</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT 0</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr"/>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Nombre de femmes concernées — donnée agrégée uniquement, pas de liste individuelle à ce stade</t>
+          <t>Période prévue pour l'activité financée</t>
         </is>
       </c>
     </row>
@@ -2632,23 +2660,23 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>nb_hommes_benef</t>
+          <t>site_travail</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>VARCHAR(150)</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT 0</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr"/>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Nombre d'hommes concernés — donnée agrégée uniquement</t>
+          <t>Lieu où se déroule l'activité</t>
         </is>
       </c>
     </row>
@@ -2660,23 +2688,23 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>montant_demande</t>
+          <t>nb_femmes_benef</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NOT NULL, DEFAULT 0</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr"/>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Budget demandé</t>
+          <t>Nombre de femmes concernées — donnée agrégée uniquement, pas de liste individuelle à ce stade</t>
         </is>
       </c>
     </row>
@@ -2688,23 +2716,23 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>co_financement_en_nature</t>
+          <t>nb_hommes_benef</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n"/>
+          <t>NOT NULL, DEFAULT 0</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr"/>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Apport du canton en nature (matériel, main d'oeuvre...) — rassure le donateur sur l'implication locale (demande du président)</t>
+          <t>Nombre d'hommes concernés — donnée agrégée uniquement</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2744,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>co_financement_especes</t>
+          <t>montant_demande</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -2726,13 +2754,13 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="n"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr"/>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Apport du canton en espèces — même objectif (demande du président)</t>
+          <t>Budget demandé</t>
         </is>
       </c>
     </row>
@@ -2744,23 +2772,23 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>statut_global</t>
+          <t>co_financement_en_nature</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DECIMAL(15,2)</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT 'EnCours'</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n"/>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>EnCours, EnAttenteResponsable (comité a valide en interne, en attente de decision de la Responsable), Validee, Rejetee</t>
+          <t>Apport du canton en nature (matériel, main d'oeuvre...) — rassure le donateur sur l'implication locale (demande du président)</t>
         </is>
       </c>
     </row>
@@ -2772,107 +2800,107 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>date_creation</t>
+          <t>co_financement_especes</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DECIMAL(15,2)</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n"/>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Date de soumission de la demande</t>
+          <t>Apport du canton en espèces — même objectif (demande du président)</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>financement</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>demande_financement</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>statut_global</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
+          <t>NOT NULL, DEFAULT 'EnCours'</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>EnCours, EnAttenteResponsable (comité a valide en interne, en attente de decision de la Responsable), Validee, Rejetee</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>financement</t>
+          <t>demande_financement</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>code_financement</t>
+          <t>date_creation</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(50)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>UNIQUE, NOT NULL</t>
+          <t>NOT NULL, DEFAULT CURRENT_TIMESTAMP</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr"/>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Numéro généré automatiquement par le système, format NOM_PROG/AJT/FR/ANNEE/No_Ordre (ex. COMDEKS4/AJT/FR/2026/00014), confirmé par le président</t>
+          <t>Date de soumission de la demande</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>financement</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>reference_utilisateur</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(100)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="n"/>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Référence saisie manuellement par l'utilisateur (usage exact — numéro de dossier physique ou bailleur — à confirmer avec le président)</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -2884,12 +2912,12 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>demande_financement_id</t>
+          <t>code_financement</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(50)</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -2897,14 +2925,10 @@
           <t>UNIQUE, NOT NULL</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>demande_financement.id</t>
-        </is>
-      </c>
+      <c r="E86" s="3" t="inlineStr"/>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>La demande validée qui a généré ce financement — UNIQUE garantit qu'une demande ne génère jamais plus d'un financement</t>
+          <t>Numéro généré automatiquement par le système, format NOM_PROG/AJT/FR/ANNEE/No_Ordre (ex. COMDEKS4/AJT/FR/2026/00014), confirmé par le président</t>
         </is>
       </c>
     </row>
@@ -2916,27 +2940,23 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>fond_rotatif_id</t>
+          <t>reference_utilisateur</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>fond_rotatif.id</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n"/>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Le fonds débité par ce financement</t>
+          <t>Référence saisie manuellement par l'utilisateur (usage exact — numéro de dossier physique ou bailleur — à confirmer avec le président)</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2968,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>programme_id</t>
+          <t>demande_financement_id</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -2958,17 +2978,17 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>UNIQUE, NOT NULL</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>programme.id</t>
+          <t>demande_financement.id</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Programme ayant financé cette part précise (COMDEKS4 ou autre) — utilisé aussi pour générer le préfixe NOM_PROG du code_financement</t>
+          <t>La demande validée qui a généré ce financement — UNIQUE garantit qu'une demande ne génère jamais plus d'un financement</t>
         </is>
       </c>
     </row>
@@ -2980,7 +3000,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>responsable_id</t>
+          <t>fond_rotatif_id</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -2995,12 +3015,12 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>responsable_fond_rotatif.id</t>
+          <t>fond_rotatif.id</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Qui a attribué/décaissé (niveau 2 : validation finale par la Responsable)</t>
+          <t>Le fonds débité par ce financement</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3032,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>montant_financement</t>
+          <t>programme_id</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -3025,10 +3045,14 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>programme.id</t>
+        </is>
+      </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>Montant total décaissé au comité</t>
+          <t>Programme ayant financé cette part précise (COMDEKS4 ou autre) — utilisé aussi pour générer le préfixe NOM_PROG du code_financement</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3064,12 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>taux_majoration_applique</t>
+          <t>responsable_id</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(5,2)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -3053,10 +3077,14 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="E91" s="3" t="n"/>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>responsable_fond_rotatif.id</t>
+        </is>
+      </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Majoration appliquée (ex. 10.00%), figée au moment du décaissement pour ne pas affecter rétroactivement les prêts en cours si le taux change (voir table parametre)</t>
+          <t>Qui a attribué/décaissé (niveau 2 : validation finale par la Responsable)</t>
         </is>
       </c>
     </row>
@@ -3068,12 +3096,12 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>date_decaissement</t>
+          <t>montant_financement</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>DECIMAL(15,2)</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -3084,7 +3112,7 @@
       <c r="E92" s="3" t="inlineStr"/>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Date du décaissement effectif</t>
+          <t>Montant total décaissé au comité</t>
         </is>
       </c>
     </row>
@@ -3096,95 +3124,91 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>statut</t>
+          <t>taux_majoration_applique</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DECIMAL(5,2)</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT 'Actif'</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr"/>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>Actif, Clôturé, TotalementDistribué</t>
+          <t>Majoration appliquée (ex. 10.00%), figée au moment du décaissement pour ne pas affecter rétroactivement les prêts en cours si le taux change (voir table parametre)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>attribution_financement</t>
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>financement</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>date_decaissement</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr"/>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Date du décaissement effectif</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
         <is>
+          <t>financement</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT 'Actif'</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr"/>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>Actif, Clôturé, TotalementDistribué</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
           <t>attribution_financement</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>financement_id</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL, UNIQUE avec beneficiaire_id</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>financement.id</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>Le financement dont est issue cette part individuelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>attribution_financement</t>
-        </is>
-      </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>beneficiaire_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -3194,17 +3218,13 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, UNIQUE avec financement_id</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>beneficiaire.id</t>
-        </is>
-      </c>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Le bénéficiaire qui reçoit cette part — un bénéficiaire ne reçoit qu'une seule part par financement</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -3216,23 +3236,27 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>montant_attribue</t>
+          <t>financement_id</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr"/>
+          <t>NOT NULL, UNIQUE avec beneficiaire_id</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>financement.id</t>
+        </is>
+      </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Part individuelle du financement global — classe-association issue de la répartition Financement ↔ Beneficiaire</t>
+          <t>Le financement dont est issue cette part individuelle</t>
         </is>
       </c>
     </row>
@@ -3244,111 +3268,111 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>date_attribution</t>
+          <t>beneficiaire_id</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr"/>
+          <t>NOT NULL, UNIQUE avec financement_id</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire.id</t>
+        </is>
+      </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Date d'enregistrement de la répartition</t>
+          <t>Le bénéficiaire qui reçoit cette part — un bénéficiaire ne reçoit qu'une seule part par financement</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>remboursement_beneficiaire</t>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>attribution_financement</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>montant_attribue</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DECIMAL(15,2)</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr"/>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Part individuelle du financement global — classe-association issue de la répartition Financement ↔ Beneficiaire</t>
         </is>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="3" t="inlineStr">
         <is>
+          <t>attribution_financement</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>date_attribution</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr"/>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>Date d'enregistrement de la répartition</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
           <t>remboursement_beneficiaire</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>attribution_financement_id</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>attribution_financement.id</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>La part précise que ce remboursement rembourse — niveau individuel, pas de circuit de Validation (gestion interne libre du comité)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>remboursement_beneficiaire</t>
-        </is>
-      </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>montant</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr"/>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>Montant versé par le bénéficiaire au comité</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -3360,12 +3384,12 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>date_versement</t>
+          <t>attribution_financement_id</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
@@ -3373,10 +3397,14 @@
           <t>NOT NULL</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr"/>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>attribution_financement.id</t>
+        </is>
+      </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Date du versement — fait déjà accompli au moment de l'enregistrement</t>
+          <t>La part précise que ce remboursement rembourse — niveau individuel, pas de circuit de Validation (gestion interne libre du comité)</t>
         </is>
       </c>
     </row>
@@ -3388,139 +3416,135 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>observation</t>
+          <t>montant</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>DECIMAL(15,2)</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Remarques éventuelles</t>
+          <t>Montant versé par le bénéficiaire au comité</t>
         </is>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>remboursement_collectif</t>
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>remboursement_beneficiaire</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>date_versement</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr"/>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Date du versement — fait déjà accompli au moment de l'enregistrement</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>remboursement_collectif</t>
+          <t>remboursement_beneficiaire</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>financement_id</t>
+          <t>observation</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, UNIQUE avec numero_semaine</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>financement.id</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr"/>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Le financement remboursé collectivement au fonds</t>
+          <t>Remarques éventuelles</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
+          <t>remboursement_beneficiaire</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT 'EnAttente'</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n"/>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>EnAttente / Confirme / Rejete — double validation : le comité enregistre le versement, mais seul un remboursement Confirme par le Trésorier compte dans la situation financière du bénéficiaire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
           <t>remboursement_collectif</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>numero_semaine</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL, UNIQUE avec financement_id</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr"/>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>Semaine du calendrier de remboursement — une seule ligne par semaine et par financement</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>remboursement_collectif</t>
-        </is>
-      </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>date_prevue</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Date à laquelle le versement était attendu</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -3532,23 +3556,27 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>date_paiement</t>
+          <t>financement_id</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr"/>
+          <t>NOT NULL, UNIQUE avec numero_semaine</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>financement.id</t>
+        </is>
+      </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Date réelle du versement — NULL tant que non payé</t>
+          <t>Le financement remboursé collectivement au fonds</t>
         </is>
       </c>
     </row>
@@ -3560,23 +3588,23 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>montant_prevu</t>
+          <t>numero_semaine</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NOT NULL, UNIQUE avec financement_id</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Montant attendu pour cette échéance</t>
+          <t>Semaine du calendrier de remboursement — une seule ligne par semaine et par financement</t>
         </is>
       </c>
     </row>
@@ -3588,23 +3616,23 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>montant_verse</t>
+          <t>date_prevue</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E110" s="3" t="inlineStr"/>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>Montant réellement versé — NULL tant que non confirmé</t>
+          <t>Date à laquelle le versement était attendu</t>
         </is>
       </c>
     </row>
@@ -3616,23 +3644,23 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>statut</t>
+          <t>date_paiement</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT 'EnAttente'</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr"/>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>EnAttente, Confirmé, Rejeté, EnRetard — niveau collectif protégé par le circuit de Validation à 3 niveaux</t>
+          <t>Date réelle du versement — NULL tant que non payé</t>
         </is>
       </c>
     </row>
@@ -3644,183 +3672,175 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>observation</t>
+          <t>montant_prevu</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>DECIMAL(15,2)</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr"/>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>Remarques éventuelles</t>
+          <t>Montant attendu pour cette échéance</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>validation</t>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>remboursement_collectif</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>montant_verse</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DECIMAL(15,2)</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr"/>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>Montant réellement versé — NULL tant que non confirmé</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>remboursement_collectif</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>demande_financement_id</t>
+          <t>statut</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>NULL (voir CHECK)</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>demande_financement.id</t>
-        </is>
-      </c>
+          <t>NOT NULL, DEFAULT 'EnAttente'</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr"/>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>Rempli uniquement si cette validation porte sur une demande de financement</t>
+          <t>EnAttente, Confirmé, Rejeté, EnRetard — niveau collectif protégé par le circuit de Validation à 3 niveaux</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>remboursement_collectif</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>remboursement_collectif_id</t>
+          <t>observation</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>NULL (voir CHECK)</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>remboursement_collectif.id</t>
-        </is>
-      </c>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr"/>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Rempli uniquement si cette validation porte sur un remboursement collectif</t>
+          <t>Remarques éventuelles</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>remboursement_collectif</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>niveau</t>
+          <t>rappel_envoye</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr"/>
+          <t>NOT NULL, DEFAULT FALSE</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n"/>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>TRESORIER (niveau 0), COMMISSAIRE (niveau 1), PRESIDENT (niveau 2) — confirmé par le président</t>
+          <t>Empêche l'envoi en double du rappel automatique à J-3 avant l'échéance (job planifié, module Notifications).</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
+          <t>remboursement_collectif</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>rappel_jour_j_envoye</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT FALSE</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n"/>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Empêche l'envoi en double du rappel automatique le jour même de l'échéance (job planifié, module Notifications).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
           <t>validation</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>ordre</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>SMALLINT</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr"/>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>0, 1, 2 — garantit le respect de la séquence du circuit</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>validation</t>
-        </is>
-      </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>membre_comite_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -3830,17 +3850,13 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>membre_comite.id</t>
-        </is>
-      </c>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr"/>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>Qui a traité cette étape — NULL tant que l'étape est en attente, rempli au moment du traitement (approbation/rejet)</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -3852,23 +3868,27 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>statut</t>
+          <t>demande_financement_id</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>VARCHAR(20)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT 'EnAttente'</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr"/>
+          <t>NULL (voir CHECK)</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>demande_financement.id</t>
+        </is>
+      </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>EnAttente, Approuvé, Rejeté</t>
+          <t>Rempli uniquement si cette validation porte sur une demande de financement</t>
         </is>
       </c>
     </row>
@@ -3880,23 +3900,27 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>commentaire</t>
+          <t>remboursement_collectif_id</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr"/>
+          <t>NULL (voir CHECK)</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>remboursement_collectif.id</t>
+        </is>
+      </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Justification, notamment en cas de rejet</t>
+          <t>Rempli uniquement si cette validation porte sur un remboursement collectif</t>
         </is>
       </c>
     </row>
@@ -3908,191 +3932,195 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>date_traitement</t>
+          <t>niveau</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Rempli seulement une fois l'étape traitée. CONTRAINTE CHECK : exactement un des deux FK (demande OU remboursement) doit être rempli, jamais les deux ni aucun</t>
+          <t>TRESORIER (niveau 0), COMMISSAIRE (niveau 1), PRESIDENT (niveau 2) — confirmé par le président</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>rapport_genere</t>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>validation</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>ordre</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>SMALLINT</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>PK, AUTO_INCREMENT</t>
+          <t>NOT NULL</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr"/>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>Identifiant technique</t>
+          <t>0, 1, 2 — garantit le respect de la séquence du circuit</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>rapport_genere</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>date_generation</t>
+          <t>membre_comite_id</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL, DEFAULT CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr"/>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>membre_comite.id</t>
+        </is>
+      </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Moment où l'instantané a été pris</t>
+          <t>Qui a traité cette étape — NULL tant que l'étape est en attente, rempli au moment du traitement (approbation/rejet)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>rapport_genere</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>periode_debut</t>
+          <t>statut</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR(20)</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NOT NULL, DEFAULT 'EnAttente'</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr"/>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Début de la période couverte par le rapport</t>
+          <t>EnAttente, Approuvé, Rejeté</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>rapport_genere</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>periode_fin</t>
+          <t>commentaire</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Fin de la période couverte</t>
+          <t>Justification, notamment en cas de rejet</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>rapport_genere</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>nombre_beneficiaires</t>
+          <t>date_traitement</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NULL</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr"/>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Instantané figé au moment de la génération — pas recalculé après coup</t>
+          <t>Rempli seulement une fois l'étape traitée. CONTRAINTE CHECK : exactement un des deux FK (demande OU remboursement) doit être rempli, jamais les deux ni aucun</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>rapport_genere</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>montant_total_finance</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>PK, AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr"/>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Instantané figé</t>
+          <t>Identifiant technique</t>
         </is>
       </c>
     </row>
@@ -4104,23 +4132,23 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>montant_total_rembourse</t>
+          <t>date_generation</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(15,2)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>NOT NULL</t>
+          <t>NOT NULL, DEFAULT CURRENT_TIMESTAMP</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr"/>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>Instantané figé</t>
+          <t>Moment où l'instantané a été pris</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4160,12 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>taux_remboursement</t>
+          <t>periode_debut</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>DECIMAL(5,2)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
@@ -4148,7 +4176,7 @@
       <c r="E129" s="3" t="inlineStr"/>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Instantané figé</t>
+          <t>Début de la période couverte par le rapport</t>
         </is>
       </c>
     </row>
@@ -4160,12 +4188,12 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>nombre_retards</t>
+          <t>periode_fin</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
@@ -4176,7 +4204,7 @@
       <c r="E130" s="3" t="inlineStr"/>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Instantané figé</t>
+          <t>Fin de la période couverte</t>
         </is>
       </c>
     </row>
@@ -4188,27 +4216,1455 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
+          <t>nombre_beneficiaires</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr"/>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>Instantané figé au moment de la génération — pas recalculé après coup</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>rapport_genere</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>montant_total_finance</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>DECIMAL(15,2)</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr"/>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>Instantané figé</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>rapport_genere</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>montant_total_rembourse</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>DECIMAL(15,2)</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr"/>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Instantané figé</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>rapport_genere</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>taux_remboursement</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>DECIMAL(5,2)</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr"/>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>Instantané figé</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>rapport_genere</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>nombre_retards</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr"/>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>Instantané figé</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>rapport_genere</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
           <t>genere_par</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>NOT NULL</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>responsable_fond_rotatif.id</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>Qui a généré ce rapport — répond au besoin du module Reporting du cahier des charges</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>autorite</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="n"/>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>Identifiant technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>autorite</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>utilisateur_id</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>UNIQUE, NOT NULL</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>utilisateur.id</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>Héritage Autorite → Utilisateur (relation 1-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>autorite</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>fonction</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(150)</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="n"/>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>Libellé libre du poste occupé, ex. "Délégué départemental de la Jeunesse" — les fonctions d'autorité sont trop variées pour une table de référence fermée comme fonction (module comité).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>autorite</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>type_critere</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>ENUM('DOMAINE','SEXE','AGE_MAX')</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="n"/>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>Détermine quelle statistique l'autorité peut consulter (module Autorités/Statistiques) : par domaine d'activité, par sexe, ou par tranche d'âge maximum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>autorite</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>domaine_id</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>domaine.id</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>Renseigné uniquement si type_critere = DOMAINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>autorite</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>valeur_critere</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(20)</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n"/>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>Renseigné uniquement si type_critere = SEXE ('F'/'M') ou AGE_MAX (ex. '30') — la valeur du critère de filtrage des statistiques auxquelles cette autorité a accès.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>autorite</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT TRUE</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="n"/>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>Permet de désactiver une autorité sans la supprimer</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>demande_beneficiaire_prevu</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="n"/>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>Identifiant technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>demande_beneficiaire_prevu</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>demande_financement_id</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>demande_financement.id</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>La demande de financement à laquelle ce bénéficiaire prévisionnel est rattaché.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>demande_beneficiaire_prevu</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire_id</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire.id</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>Renseigné si le bénéficiaire a déjà un compte au moment de la demande (le comité le choisit dans la liste existante).</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>demande_beneficiaire_prevu</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>nom_libre</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(150)</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="n"/>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>Renseigné si le bénéficiaire n'a pas encore de compte au moment de la demande (juste son nom, en attendant que le comité crée réellement son compte) — la demande liste qui est prévu pour être aidé, avant même l'attribution effective.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>groupe_mmf</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="n"/>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>Identifiant technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>groupe_mmf</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(150)</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="n"/>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>Nom du groupe de solidarité MMF</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>groupe_mmf</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>canton_id</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>canton.id</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>Un groupe MMF est toujours rattaché à un seul canton</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>groupe_mmf</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>responsable_beneficiaire_id</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire.id</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Le bénéficiaire responsable élu par les membres du groupe (module 2 du cahier des charges) — NULL tant qu'aucun responsable n'a encore été désigné.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>groupe_mmf</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>date_creation</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Date de création du groupe</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>groupe_mmf</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT TRUE</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n"/>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Permet de dissoudre un groupe sans le supprimer (historique des cotisations conservé)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>adhesion_groupe</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n"/>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>Identifiant technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>adhesion_groupe</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>groupe_mmf_id</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>groupe_mmf.id</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>Le groupe auquel le bénéficiaire adhère</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>adhesion_groupe</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire_id</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire.id</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>Le bénéficiaire membre du groupe</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>adhesion_groupe</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>date_adhesion</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="n"/>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>Date d'entrée dans le groupe</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>adhesion_groupe</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>actif</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT TRUE</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="n"/>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>Permet de faire sortir un bénéficiaire du groupe sans supprimer l'historique de ses cotisations passées. Contrainte UNIQUE(groupe_mmf_id, beneficiaire_id) : un bénéficiaire n'adhère qu'une fois au même groupe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>cotisation</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n"/>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>Identifiant technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>cotisation</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>code_cotisation</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(30)</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>UNIQUE, NOT NULL</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>Identifiant métier lisible du versement (reçu PDF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>cotisation</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>groupe_mmf_id</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>groupe_mmf.id</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>Le groupe au sein duquel la cotisation est versée</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>cotisation</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire_id</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire.id</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>Le bénéficiaire qui cotise</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>cotisation</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>montant</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>DECIMAL(15,2)</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="n"/>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>Montant versé</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>cotisation</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>date_versement</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="n"/>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>Date du versement</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>cotisation</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>observation</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="n"/>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>Remarques éventuelles</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>cotisation</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>enregistre_par</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>membre_comite.id</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>Le membre du comité qui a enregistré le versement — traçabilité de la collecte sur le terrain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>cotisation</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>annulee</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT FALSE</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="n"/>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>Annulation logique plutôt que suppression, ex. erreur de saisie — la cotisation reste visible dans l'historique avec son motif.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>cotisation</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>motif_annulation</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(255)</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="n"/>
+      <c r="F168" s="3" t="inlineStr">
+        <is>
+          <t>Renseigné uniquement si annulee = TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>conseiller_ia_historique</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="n"/>
+      <c r="F169" s="3" t="inlineStr">
+        <is>
+          <t>Identifiant technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>conseiller_ia_historique</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire_id</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>beneficiaire.id</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="inlineStr">
+        <is>
+          <t>Renseigné quand l'échange porte sur un bénéficiaire précis : le bénéficiaire lui-même (Mobile) ou un membre du comité consultant un bénéficiaire de son canton (Mobile).</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>conseiller_ia_historique</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>canton_id</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>canton.id</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>Renseigné quand l'échange porte sur un canton entier : la Responsable (Web), qui supervise plusieurs cantons et consulte une vue agrégée plutôt qu'un bénéficiaire précis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>conseiller_ia_historique</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="n"/>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>La question posée à l'IA, ou le libellé conventionnel "Analyse financière complète" pour une analyse en 4 sections plutôt qu'une question libre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>conseiller_ia_historique</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>reponse</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="n"/>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>Réponse générée par l'IA (API Gemini), à partir du contexte financier réel du bénéficiaire ou du canton concerné.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>conseiller_ia_historique</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>date_creation</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="n"/>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>Date de l'échange</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>PK, AUTO_INCREMENT</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="n"/>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>Identifiant technique</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>utilisateur_id</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>utilisateur.id</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>Le destinataire de la notification (bénéficiaire, membre du comité, ou Responsable selon le cas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>VARCHAR(150)</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="n"/>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>Titre court affiché en tête de la notification</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="n"/>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>Contenu détaillé du message</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>lue</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT FALSE</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="n"/>
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>Permet de distinguer les notifications déjà consultées des nouvelles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>date_creation</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>NOT NULL, DEFAULT CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="n"/>
+      <c r="F180" s="3" t="inlineStr">
+        <is>
+          <t>Date de génération de la notification (ex. rappel d'échéance automatique).</t>
         </is>
       </c>
     </row>
